--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484251_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484251_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5857</v>
+        <v>3.9145</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2626</v>
+        <v>5.7276</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6769</v>
+        <v>-1.8131</v>
       </c>
       <c r="G2" t="n">
         <v>2.5457</v>
@@ -610,13 +610,13 @@
         <v>3.1255</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1088</v>
+        <v>-0.78</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0756</v>
+        <v>-0.6107</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0332</v>
+        <v>-0.1694</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5392</v>
+        <v>1.2341</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0806</v>
+        <v>-0.0611</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4586</v>
+        <v>1.2952</v>
       </c>
       <c r="G3" t="n">
         <v>1.3709</v>
@@ -688,13 +688,13 @@
         <v>3.3208</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4996</v>
+        <v>-0.8047</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3548</v>
+        <v>-0.4965</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1448</v>
+        <v>-0.3083</v>
       </c>
       <c r="V3" t="n">
         <v>0.2772</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1307</v>
+        <v>0.0793</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1858</v>
+        <v>0.2869</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3166</v>
+        <v>-0.2076</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6978</v>
@@ -766,13 +766,13 @@
         <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5464</v>
+        <v>-0.3363</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4842</v>
+        <v>-0.3831</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0622</v>
+        <v>0.0467</v>
       </c>
       <c r="V4" t="n">
         <v>0.3321</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7489</v>
+        <v>-0.7907</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5867</v>
+        <v>-0.8286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8378</v>
+        <v>0.038</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.9942</v>
+        <v>-1.9847</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1717</v>
+        <v>-3.9545</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8225</v>
+        <v>1.9698</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6865</v>
+        <v>-0.0625</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0243</v>
+        <v>-1.8982</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6623</v>
+        <v>1.8358</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.6808</v>
+        <v>-1.9223</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.196</v>
+        <v>-2.0563</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4848</v>
+        <v>0.134</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.4929</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.618</v>
+        <v>-1.3454</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.7661</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0257</v>
+        <v>-0.5792</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3469</v>
+        <v>-0.988</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3266</v>
+        <v>-1.5262</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0204</v>
+        <v>0.5382</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5078</v>
+        <v>-2.9942</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5493</v>
+        <v>-2.1717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0415</v>
+        <v>-0.8225</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5442</v>
+        <v>0.6865</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0371</v>
+        <v>0.0243</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5813</v>
+        <v>0.6623</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.052</v>
+        <v>-3.6808</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5121</v>
+        <v>-2.196</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5399</v>
+        <v>-1.4848</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9301</v>
+        <v>4.4929</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5739</v>
+        <v>-0.857</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8941</v>
+        <v>-0.5831</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3201</v>
+        <v>-0.2739</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.353</v>
+        <v>-1.207</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0914</v>
+        <v>-1.0232</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2616</v>
+        <v>-0.1838</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9847</v>
+        <v>-1.5078</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.9545</v>
+        <v>-1.5493</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9698</v>
+        <v>0.0415</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0625</v>
+        <v>0.5442</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8982</v>
+        <v>-0.0371</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8358</v>
+        <v>0.5813</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9223</v>
+        <v>-2.052</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.0563</v>
+        <v>-1.5121</v>
       </c>
       <c r="O7" t="n">
-        <v>0.134</v>
+        <v>-0.5399</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5395</v>
+        <v>2.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9077</v>
+        <v>-0.434</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0289</v>
+        <v>-0.5907</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8788</v>
+        <v>0.1567</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5061</v>
+        <v>-2.0855</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4886</v>
+        <v>-1.0953</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0174</v>
+        <v>-0.9902</v>
       </c>
       <c r="G8" t="n">
         <v>-2.3063</v>
@@ -1078,13 +1078,13 @@
         <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6868</v>
+        <v>0.1074</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6357</v>
+        <v>0.029</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0511</v>
+        <v>0.0784</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2772</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0621</v>
+        <v>-2.8054</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0229</v>
+        <v>1.2251</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.085</v>
+        <v>-4.0305</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9829</v>
@@ -1156,13 +1156,13 @@
         <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.243</v>
+        <v>-0.9863</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9684</v>
+        <v>-0.7661</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2746</v>
+        <v>-0.2202</v>
       </c>
       <c r="V9" t="n">
         <v>0.5545</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9061</v>
+        <v>-3.9449</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7774</v>
+        <v>-3.9796</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1287</v>
+        <v>0.0347</v>
       </c>
       <c r="G10" t="n">
         <v>-4.8458</v>
@@ -1234,13 +1234,13 @@
         <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2129</v>
+        <v>-0.2517</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0522</v>
+        <v>-0.2544</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1607</v>
+        <v>0.0027</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9962</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3691</v>
+        <v>-4.4019</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2226</v>
+        <v>-4.3643</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1464</v>
+        <v>-0.0375</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1994</v>
@@ -1312,13 +1312,13 @@
         <v>2.5395</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6069</v>
+        <v>-0.6397</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0989</v>
+        <v>-0.2406</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.508</v>
+        <v>-0.399</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.298</v>
+        <v>-10.9955</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.941400000000001</v>
+        <v>-5.6387</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.3566</v>
+        <v>-5.356599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-14.6023</v>
@@ -1360,13 +1360,13 @@
         <v>-16.6246</v>
       </c>
       <c r="I12" t="n">
-        <v>2.022499999999999</v>
+        <v>2.0225</v>
       </c>
       <c r="J12" t="n">
         <v>10.6404</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5192000000000005</v>
+        <v>0.5192000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>10.1214</v>
@@ -1390,19 +1390,19 @@
         <v>26.3714</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.6304</v>
+        <v>-6.3277</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.965000000000001</v>
+        <v>-4.6623</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6654</v>
+        <v>-1.6655</v>
       </c>
       <c r="V12" t="n">
         <v>0.1677</v>
       </c>
       <c r="W12" t="n">
-        <v>4.987299999999999</v>
+        <v>4.9873</v>
       </c>
       <c r="X12" t="n">
         <v>-4.819599999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.9629</v>
+        <v>10.8604</v>
       </c>
       <c r="E13" t="n">
-        <v>9.0303</v>
+        <v>8.9292</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9326</v>
+        <v>1.9312</v>
       </c>
       <c r="G13" t="n">
         <v>8.9153</v>
@@ -1468,13 +1468,13 @@
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>1.747</v>
+        <v>1.6446</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5009</v>
+        <v>0.3998</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2461</v>
+        <v>1.2448</v>
       </c>
       <c r="V13" t="n">
         <v>0.8865</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8846</v>
+        <v>5.0203</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2352</v>
+        <v>3.0441</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6494</v>
+        <v>1.9763</v>
       </c>
       <c r="G14" t="n">
         <v>5.0479</v>
@@ -1546,13 +1546,13 @@
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3819</v>
+        <v>0.7538</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3444</v>
+        <v>0.6712</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8823</v>
+        <v>2.5586</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3637</v>
+        <v>2.1503</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.4084</v>
       </c>
       <c r="G15" t="n">
         <v>4.1174</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0226</v>
+        <v>1.6989</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8491</v>
+        <v>0.6357</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1735</v>
+        <v>1.0632</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1089</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4705</v>
+        <v>2.356</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4969</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9674</v>
+        <v>2.3473</v>
       </c>
       <c r="G16" t="n">
         <v>2.46</v>
@@ -1702,13 +1702,13 @@
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5988</v>
+        <v>0.2868</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.2207</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1275</v>
+        <v>0.5074</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6468</v>
+        <v>-1.0901</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8016</v>
+        <v>-1.4083</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1548</v>
+        <v>0.3182</v>
       </c>
       <c r="G17" t="n">
         <v>0.9141</v>
@@ -1780,13 +1780,13 @@
         <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4158</v>
+        <v>0.9725</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8035</v>
+        <v>0.1968</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6123</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2186</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0844</v>
+        <v>-1.5981</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6657</v>
+        <v>-2.8102</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4186</v>
+        <v>1.2121</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6745</v>
+        <v>-3.4655</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1348</v>
+        <v>0.2021</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8093</v>
+        <v>-3.6676</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1.1475</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.2264</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.3739</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6745</v>
+        <v>-2.318</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1348</v>
+        <v>-0.0243</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8093</v>
+        <v>-2.2937</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5627</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-4.1022</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1529</v>
+        <v>0.5826</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2877</v>
+        <v>0.0022</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1348</v>
+        <v>0.5804</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.4335</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.9962</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0446</v>
+        <v>-1.8933</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.364</v>
+        <v>-1.4747</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6806</v>
+        <v>-0.4186</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2559</v>
+        <v>-0.6745</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2556</v>
+        <v>0.1348</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5114</v>
+        <v>-0.8093</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6575</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4147</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2428</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9133</v>
+        <v>-0.6745</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1591</v>
+        <v>0.1348</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7542</v>
+        <v>-0.8093</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>1.348</v>
+        <v>0.3439</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1732</v>
+        <v>0.4788</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5212</v>
+        <v>-0.1348</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.16</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2111</v>
+        <v>-1.9544</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2239</v>
+        <v>-2.0217</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0128</v>
+        <v>0.0673</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4565</v>
@@ -2014,13 +2014,13 @@
         <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3406</v>
+        <v>-0.0839</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0985</v>
+        <v>-0.044</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9153</v>
+        <v>-2.2873</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7202</v>
+        <v>-1.0607</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8048999999999999</v>
+        <v>-1.2267</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4655</v>
+        <v>-0.2559</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2021</v>
+        <v>1.2556</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6676</v>
+        <v>-1.5114</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1475</v>
+        <v>1.6575</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2264</v>
+        <v>1.4147</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3739</v>
+        <v>0.2428</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.318</v>
+        <v>-1.9133</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0243</v>
+        <v>-0.1591</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2937</v>
+        <v>-1.7542</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1022</v>
+        <v>-3.1255</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7346</v>
+        <v>1.1053</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.1301</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1732</v>
+        <v>0.9751</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4335</v>
+        <v>-2.16</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9962</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>11.2981</v>
+        <v>11.9721</v>
       </c>
       <c r="E22" t="n">
-        <v>5.356899999999998</v>
+        <v>5.356700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>5.9413</v>
+        <v>6.6155</v>
       </c>
       <c r="G22" t="n">
         <v>14.6023</v>
@@ -2140,7 +2140,7 @@
         <v>16.6248</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.022200000000001</v>
+        <v>-2.022200000000002</v>
       </c>
       <c r="J22" t="n">
         <v>25.2428</v>
@@ -2170,13 +2170,13 @@
         <v>16.6042</v>
       </c>
       <c r="S22" t="n">
-        <v>6.6304</v>
+        <v>7.3045</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6655</v>
+        <v>1.6654</v>
       </c>
       <c r="U22" t="n">
-        <v>4.964899999999999</v>
+        <v>5.639</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1675</v>
@@ -2185,7 +2185,7 @@
         <v>4.819599999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-4.9873</v>
+        <v>-4.987299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484251_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484251_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,47 +549,52 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9145</v>
+        <v>3.0005</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7276</v>
+        <v>4.8136</v>
       </c>
       <c r="F2" t="n">
         <v>-1.8131</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5457</v>
+        <v>1.6318</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0148</v>
+        <v>-1.3218</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5606</v>
+        <v>2.9536</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8777</v>
+        <v>3.9637</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0463</v>
+        <v>0.7393</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8314</v>
+        <v>3.2244</v>
       </c>
       <c r="M2" t="n">
         <v>-2.332</v>
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-2.4373</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,153 +714,163 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0793</v>
+        <v>0.914</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2869</v>
+        <v>0.914</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2076</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6978</v>
+        <v>0.914</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2507</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.67</v>
+        <v>0.914</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0179</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6879</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3678</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2328</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.135</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3363</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3831</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0467</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7907</v>
+        <v>0.607</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8286</v>
+        <v>0.607</v>
       </c>
       <c r="F5" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9847</v>
+        <v>0.607</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.9545</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9698</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0625</v>
+        <v>0.607</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.8982</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8358</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9223</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.0563</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3454</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7661</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -860,714 +880,760 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.988</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5262</v>
+        <v>-0.3201</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5382</v>
+        <v>-0.2076</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9942</v>
+        <v>-1.3048</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1717</v>
+        <v>-1.2507</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8225</v>
+        <v>-0.0541</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6865</v>
+        <v>0.063</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0243</v>
+        <v>-0.0179</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6623</v>
+        <v>0.0809</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.6808</v>
+        <v>-1.3678</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.196</v>
+        <v>-1.2328</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4848</v>
+        <v>-0.135</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.4929</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.857</v>
+        <v>-0.3363</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5831</v>
+        <v>-0.3831</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2739</v>
+        <v>0.0467</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4959</v>
+        <v>0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.207</v>
+        <v>-0.7907</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0232</v>
+        <v>-0.8286</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1838</v>
+        <v>0.038</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5078</v>
+        <v>-1.9847</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5493</v>
+        <v>-3.9545</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0415</v>
+        <v>1.9698</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5442</v>
+        <v>-0.0625</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0371</v>
+        <v>-1.8982</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5813</v>
+        <v>1.8358</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.052</v>
+        <v>-1.9223</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5121</v>
+        <v>-2.0563</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5399</v>
+        <v>0.134</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9301</v>
+        <v>2.5395</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.434</v>
+        <v>-1.3454</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5907</v>
+        <v>-0.7661</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1567</v>
+        <v>-0.5792</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0855</v>
+        <v>-0.988</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0953</v>
+        <v>-1.5262</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9902</v>
+        <v>0.5382</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3063</v>
+        <v>-2.9942</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2696</v>
+        <v>-2.1717</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0367</v>
+        <v>-0.8225</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0244</v>
+        <v>0.6865</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5771</v>
+        <v>0.0243</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5527</v>
+        <v>0.6623</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3308</v>
+        <v>-3.6808</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8468</v>
+        <v>-2.196</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.484</v>
+        <v>-1.4848</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>4.4929</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1074</v>
+        <v>-0.857</v>
       </c>
       <c r="T8" t="n">
-        <v>0.029</v>
+        <v>-0.5831</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0784</v>
+        <v>-0.2739</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8054</v>
+        <v>-1.207</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2251</v>
+        <v>-1.0232</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0305</v>
+        <v>-0.1838</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9829</v>
+        <v>-1.5078</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5526</v>
+        <v>-1.5493</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4303</v>
+        <v>0.0415</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3669</v>
+        <v>0.5442</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6385</v>
+        <v>-0.0371</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7284</v>
+        <v>0.5813</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.3498</v>
+        <v>-2.052</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1911</v>
+        <v>-1.5121</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1587</v>
+        <v>-0.5399</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9863</v>
+        <v>-0.434</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7661</v>
+        <v>-0.5907</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2202</v>
+        <v>0.1567</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5545</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9449</v>
+        <v>-2.0855</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9796</v>
+        <v>-1.0953</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0347</v>
+        <v>-0.9902</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.8458</v>
+        <v>-2.3063</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7125</v>
+        <v>-0.2696</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1332</v>
+        <v>-2.0367</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.5336</v>
+        <v>1.0244</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.6145</v>
+        <v>1.5771</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>-0.5527</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3121</v>
+        <v>-3.3308</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.098</v>
+        <v>-1.8468</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2142</v>
+        <v>-1.484</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3441</v>
+        <v>2.5395</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2517</v>
+        <v>0.1074</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2544</v>
+        <v>0.029</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0027</v>
+        <v>0.0784</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9962</v>
+        <v>-0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9962</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4019</v>
+        <v>-2.8054</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3643</v>
+        <v>1.2251</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0375</v>
+        <v>-4.0305</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1994</v>
+        <v>-1.9829</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3218</v>
+        <v>-0.5526</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8776</v>
+        <v>-1.4303</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0215</v>
+        <v>2.3669</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2239</v>
+        <v>1.6385</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2023</v>
+        <v>0.7284</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1779</v>
+        <v>-4.3498</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.098</v>
+        <v>-2.1911</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0799</v>
+        <v>-2.1587</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.1022</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6397</v>
+        <v>-0.9863</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2406</v>
+        <v>-0.7661</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.399</v>
+        <v>-0.2202</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.9955</v>
+        <v>-3.9449</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6387</v>
+        <v>-3.9796</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.356599999999999</v>
+        <v>0.0347</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.6023</v>
+        <v>-4.8458</v>
       </c>
       <c r="H12" t="n">
-        <v>-16.6246</v>
+        <v>-3.7125</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0225</v>
+        <v>-1.1332</v>
       </c>
       <c r="J12" t="n">
-        <v>10.6404</v>
+        <v>-2.5336</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5192000000000001</v>
+        <v>-2.6145</v>
       </c>
       <c r="L12" t="n">
-        <v>10.1214</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-25.2429</v>
+        <v>-2.3121</v>
       </c>
       <c r="N12" t="n">
-        <v>-17.1438</v>
+        <v>-1.098</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.0991</v>
+        <v>-1.2142</v>
       </c>
       <c r="P12" t="n">
-        <v>9.767300000000001</v>
+        <v>2.1488</v>
       </c>
       <c r="Q12" t="n">
-        <v>-16.6041</v>
+        <v>-0.1953</v>
       </c>
       <c r="R12" t="n">
-        <v>26.3714</v>
+        <v>2.3441</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.3277</v>
+        <v>-0.2517</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.6623</v>
+        <v>-0.2544</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6655</v>
+        <v>0.0027</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1677</v>
+        <v>-0.9962</v>
       </c>
       <c r="W12" t="n">
-        <v>4.9873</v>
+        <v>-0.9962</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.819599999999999</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.8604</v>
+        <v>-4.4019</v>
       </c>
       <c r="E13" t="n">
-        <v>8.9292</v>
+        <v>-4.3643</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9312</v>
+        <v>-0.0375</v>
       </c>
       <c r="G13" t="n">
-        <v>8.9153</v>
+        <v>-2.1994</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2239</v>
+        <v>-1.3218</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6915</v>
+        <v>-0.8776</v>
       </c>
       <c r="J13" t="n">
-        <v>10.7683</v>
+        <v>-0.0215</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7273</v>
+        <v>-0.2239</v>
       </c>
       <c r="L13" t="n">
-        <v>7.041</v>
+        <v>0.2023</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.853</v>
+        <v>-2.1779</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5034</v>
+        <v>-1.098</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3496</v>
+        <v>-1.0799</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1255</v>
+        <v>-4.1022</v>
       </c>
       <c r="R13" t="n">
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6446</v>
+        <v>-0.6397</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3998</v>
+        <v>-0.2406</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2448</v>
+        <v>-0.399</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0203</v>
+        <v>-10.9955</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0441</v>
+        <v>-5.6387</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9763</v>
+        <v>-5.356599999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>5.0479</v>
+        <v>-14.6022</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2242</v>
+        <v>-16.6246</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8237</v>
+        <v>2.022500000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>6.0869</v>
+        <v>10.6404</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3183</v>
+        <v>0.5191999999999997</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7686</v>
+        <v>10.1214</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.039</v>
+        <v>-25.24290000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0941</v>
+        <v>-17.1438</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9449</v>
+        <v>-8.0991</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7814</v>
+        <v>9.767300000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1255</v>
+        <v>-16.6041</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3441</v>
+        <v>26.3714</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7538</v>
+        <v>-6.327699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.08260000000000001</v>
+        <v>-4.6623</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6712</v>
+        <v>-1.6655</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1677000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.987299999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-4.819599999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5586</v>
+        <v>8.4185</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1503</v>
+        <v>6.4873</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4084</v>
+        <v>1.9312</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1174</v>
+        <v>6.4734</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4534</v>
+        <v>1.9959</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.336</v>
+        <v>4.4775</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4214</v>
+        <v>8.3264</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1382</v>
+        <v>2.4994</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2833</v>
+        <v>5.8271</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.304</v>
+        <v>-1.853</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3152</v>
+        <v>-0.5034</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6192</v>
+        <v>-1.3496</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1488</v>
+        <v>-0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9069</v>
+        <v>-3.1255</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6989</v>
+        <v>1.6446</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6357</v>
+        <v>0.3998</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0632</v>
+        <v>1.2448</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1089</v>
+        <v>0.8865</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1089</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.356</v>
+        <v>5.0203</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008699999999999999</v>
+        <v>3.0441</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3473</v>
+        <v>1.9763</v>
       </c>
       <c r="G16" t="n">
-        <v>2.46</v>
+        <v>5.0479</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9742</v>
+        <v>4.2242</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4858</v>
+        <v>0.8237</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1595</v>
+        <v>6.0869</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8637</v>
+        <v>4.3183</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2959</v>
+        <v>1.7686</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6996</v>
+        <v>-1.039</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1105</v>
+        <v>-0.0941</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8101</v>
+        <v>-0.9449</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>-3.1255</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2868</v>
+        <v>0.7538</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2207</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5074</v>
+        <v>0.6712</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1718,12 +1789,17 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0901</v>
+        <v>2.5586</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4083</v>
+        <v>2.1503</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3182</v>
+        <v>0.4084</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9141</v>
+        <v>4.1174</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0432</v>
+        <v>5.4534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9574</v>
+        <v>-1.336</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2785</v>
+        <v>5.4214</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4553</v>
+        <v>5.1382</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.2833</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3643</v>
+        <v>-1.304</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4986</v>
+        <v>0.3152</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1342</v>
+        <v>-1.6192</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7581</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1022</v>
+        <v>-3.9069</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9725</v>
+        <v>1.6989</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1968</v>
+        <v>0.6357</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.0632</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>-1.1089</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4373</v>
+        <v>-1.1089</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5981</v>
+        <v>2.4419</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8102</v>
+        <v>2.4419</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2121</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.4655</v>
+        <v>2.4419</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2021</v>
+        <v>1.2279</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.6676</v>
+        <v>1.214</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1475</v>
+        <v>2.4419</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2264</v>
+        <v>1.2279</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3739</v>
+        <v>1.214</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.318</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0243</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2937</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5826</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0022</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5804</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3.4335</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.9962</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8933</v>
+        <v>2.356</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4747</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4186</v>
+        <v>2.3473</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6745</v>
+        <v>2.46</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1348</v>
+        <v>1.9742</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8093</v>
+        <v>0.4858</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.1595</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.8637</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.2959</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6745</v>
+        <v>-0.6996</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1348</v>
+        <v>0.1105</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8093</v>
+        <v>-0.8101</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3439</v>
+        <v>0.2868</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4788</v>
+        <v>-0.2207</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1348</v>
+        <v>0.5074</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. COSTA RABANEDA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9544</v>
+        <v>-1.0901</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0217</v>
+        <v>-1.4083</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0673</v>
+        <v>0.3182</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4565</v>
+        <v>0.9141</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1998</v>
+        <v>-0.0432</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6563</v>
+        <v>0.9574</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9818</v>
+        <v>1.2785</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9818</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4747</v>
+        <v>-0.3643</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1998</v>
+        <v>-0.4986</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6745</v>
+        <v>0.1342</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.1022</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0839</v>
+        <v>0.9725</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0399</v>
+        <v>0.1968</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.044</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2873</v>
+        <v>-1.5981</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0607</v>
+        <v>-2.8102</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2267</v>
+        <v>1.2121</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2559</v>
+        <v>-3.4655</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2556</v>
+        <v>0.2021</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5114</v>
+        <v>-3.6676</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6575</v>
+        <v>-1.1475</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4147</v>
+        <v>0.2264</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2428</v>
+        <v>-1.3739</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9133</v>
+        <v>-2.318</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1591</v>
+        <v>-0.0243</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7542</v>
+        <v>-2.2937</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>-4.1022</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1053</v>
+        <v>0.5826</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1301</v>
+        <v>0.0022</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9751</v>
+        <v>0.5804</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.16</v>
+        <v>3.4335</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4373</v>
+        <v>0.9962</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,318 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-1.8933</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.4747</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.4186</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.8093</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.8093</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.1348</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>M. COSTA RABANEDA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.9544</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.0217</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.4565</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.6563</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.9818</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.9818</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.4747</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.1998</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.0839</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.0399</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A. FALL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.2873</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.0607</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.2267</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.2559</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.2556</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.5114</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.6575</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.4147</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.9133</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.1591</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.7542</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.1053</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484251_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>11.9721</v>
       </c>
-      <c r="E22" t="n">
-        <v>5.356700000000001</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6.6155</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="E25" t="n">
+        <v>5.3567</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.615500000000001</v>
+      </c>
+      <c r="G25" t="n">
         <v>14.6023</v>
       </c>
-      <c r="H22" t="n">
-        <v>16.6248</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-2.022200000000002</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="H25" t="n">
+        <v>16.6247</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.022200000000001</v>
+      </c>
+      <c r="J25" t="n">
         <v>25.2428</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K25" t="n">
         <v>17.1439</v>
       </c>
-      <c r="L22" t="n">
-        <v>8.099</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L25" t="n">
+        <v>8.099100000000002</v>
+      </c>
+      <c r="M25" t="n">
         <v>-10.6404</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N25" t="n">
         <v>-0.5192</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O25" t="n">
         <v>-10.1213</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P25" t="n">
         <v>-9.767199999999999</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q25" t="n">
         <v>-26.3713</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R25" t="n">
         <v>16.6042</v>
       </c>
-      <c r="S22" t="n">
-        <v>7.3045</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="S25" t="n">
+        <v>7.304500000000001</v>
+      </c>
+      <c r="T25" t="n">
         <v>1.6654</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U25" t="n">
         <v>5.639</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V25" t="n">
         <v>-0.1675</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W25" t="n">
         <v>4.819599999999999</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X25" t="n">
         <v>-4.987299999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
